--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,135 +789,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>62014115</v>
-      </c>
-      <c r="B3" t="n">
-        <v>103602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1331</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Fläcklungört</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Pulmonaria officinalis</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Skogsgården, 600 m VSV , Sk</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>429515.8653116504</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6172198.525159081</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Sjöbo</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Lövestad</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>M-Sbo-0183</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2016-04-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2016-04-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Rune Gerell</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Rune Gerell</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>377619</v>
       </c>
       <c r="B2" t="n">
-        <v>105081</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377619</v>
       </c>
       <c r="B2" t="n">
-        <v>106366</v>
+        <v>106367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377619</v>
       </c>
       <c r="B2" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377619</v>
       </c>
       <c r="B2" t="n">
-        <v>106369</v>
+        <v>106373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377619</v>
       </c>
       <c r="B2" t="n">
-        <v>106373</v>
+        <v>106386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377619</v>
       </c>
       <c r="B2" t="n">
-        <v>106386</v>
+        <v>106387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377619</v>
       </c>
       <c r="B2" t="n">
-        <v>106387</v>
+        <v>106390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377619</v>
       </c>
       <c r="B2" t="n">
-        <v>106390</v>
+        <v>106404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377619</v>
       </c>
       <c r="B2" t="n">
-        <v>106404</v>
+        <v>106442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377619</v>
       </c>
       <c r="B2" t="n">
-        <v>106442</v>
+        <v>106456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377619</v>
       </c>
       <c r="B2" t="n">
-        <v>106466</v>
+        <v>106597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377619</v>
       </c>
       <c r="B2" t="n">
-        <v>106597</v>
+        <v>106598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377619</v>
       </c>
       <c r="B2" t="n">
-        <v>106598</v>
+        <v>106599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8150-2024 artfynd.xlsx
+++ b/artfynd/A 8150-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377619</v>
       </c>
       <c r="B2" t="n">
-        <v>106614</v>
+        <v>106680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
